--- a/Team-Data/2012-13/4-11-2012-13.xlsx
+++ b/Team-Data/2012-13/4-11-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -787,7 +854,7 @@
         <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -954,10 +1021,10 @@
         <v>16</v>
       </c>
       <c r="AO3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP3" t="n">
         <v>19</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>20</v>
       </c>
       <c r="AQ3" t="n">
         <v>9</v>
@@ -978,7 +1045,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
@@ -990,7 +1057,7 @@
         <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1357,7 +1424,7 @@
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -1389,61 +1456,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>0.551</v>
+        <v>0.545</v>
       </c>
       <c r="H6" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J6" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K6" t="n">
         <v>0.436</v>
       </c>
       <c r="L6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M6" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O6" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P6" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R6" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S6" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T6" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U6" t="n">
         <v>22.9</v>
       </c>
       <c r="V6" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
@@ -1458,19 +1525,19 @@
         <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
@@ -1479,16 +1546,16 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
         <v>13</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1497,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
@@ -1515,7 +1582,7 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
@@ -1527,7 +1594,7 @@
         <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
@@ -1536,10 +1603,10 @@
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-1</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
@@ -1855,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="AL8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="n">
         <v>12</v>
@@ -1864,7 +1931,7 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2061,7 +2128,7 @@
         <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2274,7 @@
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" t="n">
         <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>0.57</v>
+        <v>0.577</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
         <v>83.09999999999999</v>
@@ -2326,7 +2393,7 @@
         <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N11" t="n">
         <v>0.402</v>
@@ -2335,13 +2402,13 @@
         <v>17</v>
       </c>
       <c r="P11" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.79</v>
+        <v>0.792</v>
       </c>
       <c r="R11" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S11" t="n">
         <v>34.1</v>
@@ -2350,13 +2417,13 @@
         <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V11" t="n">
         <v>15.1</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
         <v>4.2</v>
@@ -2365,19 +2432,19 @@
         <v>4.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA11" t="n">
         <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2389,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
@@ -2404,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2413,10 +2480,10 @@
         <v>14</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
@@ -2425,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2440,7 +2507,7 @@
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2626,13 @@
         <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
       </c>
       <c r="AF12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
@@ -2607,7 +2674,7 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
         <v>5</v>
@@ -2625,7 +2692,7 @@
         <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
@@ -3117,7 +3184,7 @@
         <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
         <v>13</v>
@@ -3165,7 +3232,7 @@
         <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3305,7 +3372,7 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK16" t="n">
         <v>20</v>
@@ -3317,13 +3384,13 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
         <v>8</v>
@@ -3353,7 +3420,7 @@
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>18</v>
@@ -3672,13 +3739,13 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>14</v>
       </c>
       <c r="AM18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" t="n">
         <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654</v>
+        <v>0.662</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J21" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L21" t="n">
         <v>10.9</v>
       </c>
       <c r="M21" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O21" t="n">
         <v>16.3</v>
@@ -4164,13 +4231,13 @@
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U21" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V21" t="n">
         <v>12.1</v>
@@ -4185,40 +4252,40 @@
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AE21" t="n">
         <v>7</v>
       </c>
       <c r="AF21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG21" t="n">
         <v>7</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI21" t="n">
         <v>20</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4233,19 +4300,19 @@
         <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4254,16 +4321,16 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -4301,43 +4368,43 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F22" t="n">
         <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.734</v>
+        <v>0.731</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J22" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K22" t="n">
         <v>0.481</v>
       </c>
       <c r="L22" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
       <c r="O22" t="n">
         <v>22.5</v>
       </c>
       <c r="P22" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Q22" t="n">
         <v>0.829</v>
@@ -4346,19 +4413,19 @@
         <v>10.3</v>
       </c>
       <c r="S22" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T22" t="n">
         <v>43.6</v>
       </c>
       <c r="U22" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V22" t="n">
         <v>15.4</v>
       </c>
       <c r="W22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
         <v>7.7</v>
@@ -4373,13 +4440,13 @@
         <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4403,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM22" t="n">
         <v>17</v>
@@ -4430,19 +4497,19 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4815,7 +4882,7 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>28</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5310,7 +5377,7 @@
         <v>8</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL27" t="n">
         <v>11</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -5471,16 +5538,16 @@
         <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
         <v>4</v>
@@ -5507,10 +5574,10 @@
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5534,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="AY28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6132,7 @@
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-11-2012-13</t>
+          <t>2013-04-11</t>
         </is>
       </c>
     </row>
